--- a/data/trans_orig/IQ3005_MoAR-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Provincia-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer huevo</t>
+          <t>Menores según la edad en meses en la que empezaron a comer huevo (tasa de respuesta: 48,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -682,49 +682,49 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,58; 10,92</t>
+          <t>8,66; 10,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,66; 11,57</t>
+          <t>8,9; 11,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,44; 11,86</t>
+          <t>9,42; 11,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,29; 12,09</t>
+          <t>10,24; 12,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,64; 9,58</t>
+          <t>6,77; 9,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,99; 11,91</t>
+          <t>10,17; 11,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,52; 11,25</t>
+          <t>9,58; 11,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,8; 10,19</t>
+          <t>7,71; 10,1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +787,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,87; 11,03</t>
+          <t>8,83; 11,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,22; 16,75</t>
+          <t>11,13; 16,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,0; 12,75</t>
+          <t>9,26; 13,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,67; 12,58</t>
+          <t>9,8; 12,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,79; 11,64</t>
+          <t>8,63; 11,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,67; 10,61</t>
+          <t>8,62; 10,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,72; 11,62</t>
+          <t>9,8; 11,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,89; 15,75</t>
+          <t>10,83; 15,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,15; 11,97</t>
+          <t>9,22; 11,81</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,22 +897,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 13,86</t>
+          <t>6,47; 13,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,15; 14,21</t>
+          <t>11,15; 13,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,0; 12,0</t>
+          <t>9,0; 12,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,74; 13,35</t>
+          <t>7,45; 13,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -922,22 +922,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,66; 12,0</t>
+          <t>9,6; 12,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,6; 13,02</t>
+          <t>8,84; 13,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,29; 12,87</t>
+          <t>11,33; 12,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,85; 12,0</t>
+          <t>9,81; 12,0</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,51; 16,74</t>
+          <t>10,64; 16,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,35; 11,99</t>
+          <t>9,36; 11,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,55; 11,49</t>
+          <t>9,48; 11,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,83; 14,49</t>
+          <t>10,94; 14,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,73; 11,83</t>
+          <t>8,61; 11,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,79; 12,41</t>
+          <t>7,8; 12,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,13; 14,5</t>
+          <t>11,25; 14,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,6; 11,43</t>
+          <t>9,62; 11,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,91; 11,57</t>
+          <t>8,86; 11,53</t>
         </is>
       </c>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,24; 12,0</t>
+          <t>8,35; 12,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,24; 15,04</t>
+          <t>9,25; 14,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,72; 11,76</t>
+          <t>9,76; 11,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1147,24 +1147,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,61; 11,27</t>
+          <t>8,69; 11,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,52; 11,6</t>
+          <t>9,39; 11,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,73; 11,92</t>
+          <t>7,92; 12,03</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1227,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,5; 15,32</t>
+          <t>11,72; 15,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,7; 12,0</t>
+          <t>9,17; 12,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,29; 8,12</t>
+          <t>6,37; 8,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11,4; 13,36</t>
+          <t>11,4; 13,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,37; 11,51</t>
+          <t>8,49; 11,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,17; 10,33</t>
+          <t>6,0; 10,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,63; 13,63</t>
+          <t>11,7; 13,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,18; 11,51</t>
+          <t>9,12; 11,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,41; 8,91</t>
+          <t>6,57; 8,96</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,93; 14,24</t>
+          <t>12,0; 14,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,2; 12,58</t>
+          <t>10,19; 12,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,84; 9,3</t>
+          <t>6,82; 9,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,98; 12,67</t>
+          <t>11,08; 12,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,2; 13,64</t>
+          <t>11,23; 13,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,29; 12,39</t>
+          <t>8,16; 12,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,66; 13,04</t>
+          <t>11,59; 12,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,02; 12,82</t>
+          <t>11,0; 12,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,92; 10,53</t>
+          <t>7,9; 10,43</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,57; 10,61</t>
+          <t>7,42; 10,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,38; 12,29</t>
+          <t>10,42; 12,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1462,32 +1462,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,05; 11,5</t>
+          <t>8,94; 11,41</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,83; 12,29</t>
+          <t>9,76; 12,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,73; 11,5</t>
+          <t>8,74; 11,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,85; 10,83</t>
+          <t>8,86; 10,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,38; 11,84</t>
+          <t>10,26; 11,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,17; 10,79</t>
+          <t>9,12; 10,8</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,37; 11,95</t>
+          <t>10,46; 11,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,8; 11,99</t>
+          <t>10,76; 12,13</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,18; 10,46</t>
+          <t>9,14; 10,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,65; 11,81</t>
+          <t>10,7; 11,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,68; 11,63</t>
+          <t>10,68; 11,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,71; 9,99</t>
+          <t>8,7; 9,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,81; 11,68</t>
+          <t>10,78; 11,73</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,87; 11,62</t>
+          <t>10,9; 11,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,06; 9,94</t>
+          <t>9,05; 9,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3005_MoAR-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Provincia-trans_orig.xlsx
@@ -682,12 +682,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,66; 10,91</t>
+          <t>8,61; 10,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,9; 11,53</t>
+          <t>8,79; 11,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,27 +697,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 12,11</t>
+          <t>10,11; 12,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,77; 9,6</t>
+          <t>6,83; 9,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,17; 11,91</t>
+          <t>10,29; 11,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 11,23</t>
+          <t>9,46; 11,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,71; 10,1</t>
+          <t>7,86; 10,14</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,83; 11,05</t>
+          <t>8,93; 11,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,13; 16,78</t>
+          <t>11,16; 16,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,26; 13,12</t>
+          <t>9,2; 13,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,8; 12,72</t>
+          <t>9,75; 12,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,63; 11,6</t>
+          <t>8,78; 11,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,62; 10,55</t>
+          <t>8,6; 10,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,8; 11,62</t>
+          <t>9,85; 11,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,83; 15,09</t>
+          <t>10,75; 14,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,22; 11,81</t>
+          <t>9,2; 11,78</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,47; 13,84</t>
+          <t>6,49; 13,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,15; 13,75</t>
+          <t>11,15; 13,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,0; 12,0</t>
+          <t>8,0; 12,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,45; 13,35</t>
+          <t>7,6; 13,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,96; 12,17</t>
+          <t>10,74; 12,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,6; 12,0</t>
+          <t>9,66; 12,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,84; 13,23</t>
+          <t>8,69; 13,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,33; 12,87</t>
+          <t>11,34; 12,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,81; 12,0</t>
+          <t>9,91; 12,0</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,64; 16,57</t>
+          <t>10,65; 16,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,36; 11,92</t>
+          <t>9,49; 11,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,48; 11,51</t>
+          <t>9,56; 11,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,94; 14,52</t>
+          <t>10,91; 14,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,61; 11,67</t>
+          <t>8,61; 11,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,8; 12,11</t>
+          <t>7,81; 12,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,25; 14,47</t>
+          <t>11,25; 14,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,62; 11,52</t>
+          <t>9,57; 11,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,86; 11,53</t>
+          <t>8,96; 11,41</t>
         </is>
       </c>
     </row>
@@ -1117,17 +1117,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 12,0</t>
+          <t>7,8; 12,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,35; 12,0</t>
+          <t>8,4; 12,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,25; 14,96</t>
+          <t>9,23; 14,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1137,27 +1137,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,76; 11,77</t>
+          <t>9,72; 11,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 9,0</t>
+          <t>5,47; 9,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,69; 11,22</t>
+          <t>8,77; 11,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,39; 11,58</t>
+          <t>9,46; 11,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,92; 12,03</t>
+          <t>7,87; 12,02</t>
         </is>
       </c>
     </row>
@@ -1227,17 +1227,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,72; 15,32</t>
+          <t>11,5; 15,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9,17; 12,0</t>
+          <t>8,78; 12,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,13</t>
+          <t>6,29; 8,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1247,27 +1247,27 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,49; 11,5</t>
+          <t>8,51; 11,61</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,09</t>
+          <t>6,35; 10,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,7; 13,86</t>
+          <t>11,71; 13,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,12; 11,52</t>
+          <t>9,22; 11,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,57; 8,96</t>
+          <t>6,47; 8,95</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,0; 14,16</t>
+          <t>11,94; 14,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,19; 12,5</t>
+          <t>10,21; 12,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,82; 9,24</t>
+          <t>6,84; 9,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,08; 12,67</t>
+          <t>11,03; 12,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,23; 13,71</t>
+          <t>11,25; 13,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,16; 12,09</t>
+          <t>8,23; 12,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,59; 12,93</t>
+          <t>11,61; 12,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,0; 12,63</t>
+          <t>10,96; 12,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,9; 10,43</t>
+          <t>7,92; 10,55</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,42; 10,7</t>
+          <t>7,36; 10,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,42; 12,45</t>
+          <t>10,42; 12,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,74; 10,66</t>
+          <t>8,77; 10,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,94; 11,41</t>
+          <t>9,06; 11,45</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,76; 12,26</t>
+          <t>9,83; 12,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,74; 11,48</t>
+          <t>8,67; 11,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,86; 10,87</t>
+          <t>8,91; 10,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,26; 11,94</t>
+          <t>10,31; 11,81</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,12; 10,8</t>
+          <t>9,17; 10,84</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,46; 11,95</t>
+          <t>10,38; 11,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,76; 12,13</t>
+          <t>10,8; 12,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,14; 10,35</t>
+          <t>9,12; 10,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,7; 11,81</t>
+          <t>10,67; 11,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,68; 11,68</t>
+          <t>10,69; 11,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,7; 9,99</t>
+          <t>8,73; 10,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,78; 11,73</t>
+          <t>10,77; 11,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,9; 11,72</t>
+          <t>10,86; 11,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,05; 9,99</t>
+          <t>9,11; 9,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3005_MoAR-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Provincia-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10,85</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,39</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,27</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>12,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>9,97</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10,57</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,85</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,39</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,27</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9,44; 11,86</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10,29; 12,09</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6,64; 9,58</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>8,61; 10,95</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8,79; 11,58</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9,42; 11,72</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,11; 12,09</t>
+          <t>8,58; 10,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 9,6</t>
+          <t>8,66; 11,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,29; 11,91</t>
+          <t>9,99; 11,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,46; 11,25</t>
+          <t>9,52; 11,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,86; 10,14</t>
+          <t>7,8; 10,19</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11,26</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10,5</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,44</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>9,96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>12,82</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>10,78</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,26</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10,5</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>9,44</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,93; 11,08</t>
+          <t>9,67; 12,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,16; 16,75</t>
+          <t>8,79; 11,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,2; 13,17</t>
+          <t>8,67; 10,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 12,68</t>
+          <t>8,87; 11,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,78; 11,6</t>
+          <t>11,22; 16,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,6; 10,78</t>
+          <t>9,0; 12,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,85; 11,65</t>
+          <t>9,72; 11,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,75; 14,93</t>
+          <t>10,89; 15,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,2; 11,78</t>
+          <t>9,15; 11,97</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11,61</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,82</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11,43</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>11,11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>12,17</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,61</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,82</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>11,43</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,49; 13,85</t>
+          <t>7,74; 13,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,15; 13,8</t>
+          <t>10,96; 12,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>9,66; 12,0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>6,24; 13,86</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>11,15; 14,21</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>8,0; 12,0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>7,6; 13,43</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>10,74; 12,17</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>9,66; 12,0</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,69; 13,06</t>
+          <t>8,6; 13,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,34; 12,84</t>
+          <t>11,29; 12,87</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,91; 12,0</t>
+          <t>9,85; 12,0</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,19</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>10,37</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,79</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>13,16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>10,69</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>10,69</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12,19</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,37</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,79</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,65; 16,58</t>
+          <t>10,83; 14,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 11,93</t>
+          <t>8,73; 11,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,56; 11,51</t>
+          <t>7,79; 12,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,91; 14,6</t>
+          <t>10,51; 16,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,61; 11,8</t>
+          <t>9,35; 11,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,81; 12,38</t>
+          <t>9,55; 11,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,25; 14,31</t>
+          <t>11,13; 14,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,57; 11,57</t>
+          <t>9,6; 11,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,96; 11,41</t>
+          <t>8,91; 11,57</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,01</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,97</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,94</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>10,25</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>10,55</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,77</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10,01</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,97</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,94</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,8; 12,0</t>
+          <t>9,0; 11,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8,4; 12,0</t>
+          <t>9,72; 11,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,23; 14,85</t>
+          <t>5,23; 9,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,0; 11,5</t>
+          <t>7,2; 12,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,72; 11,76</t>
+          <t>8,24; 12,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,47; 9,0</t>
+          <t>9,24; 15,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,77; 11,19</t>
+          <t>8,61; 11,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,46; 11,59</t>
+          <t>9,52; 11,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,87; 12,02</t>
+          <t>7,73; 11,92</t>
         </is>
       </c>
     </row>
@@ -1174,32 +1174,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12,15</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10,29</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7,95</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>13,02</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>11,05</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>7,0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12,15</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10,29</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,95</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>11,4; 13,36</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>8,37; 11,51</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>6,17; 10,33</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>11,5; 15,32</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>8,78; 12,0</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>6,29; 8,07</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>11,4; 13,75</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,51; 11,61</t>
+          <t>8,7; 12,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,35; 10,43</t>
+          <t>6,29; 8,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,71; 13,7</t>
+          <t>11,63; 13,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,22; 11,53</t>
+          <t>9,18; 11,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,47; 8,95</t>
+          <t>6,41; 8,91</t>
         </is>
       </c>
     </row>
@@ -1284,32 +1284,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11,76</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11,99</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9,53</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>12,84</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>11,16</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>7,95</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11,76</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11,99</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,53</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,94; 14,06</t>
+          <t>10,98; 12,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,21; 12,59</t>
+          <t>11,2; 13,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,84; 9,31</t>
+          <t>8,29; 12,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,03; 12,64</t>
+          <t>11,93; 14,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,25; 13,81</t>
+          <t>10,2; 12,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,23; 12,04</t>
+          <t>6,84; 9,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,61; 12,99</t>
+          <t>11,66; 13,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,96; 12,51</t>
+          <t>11,02; 12,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7,92; 10,55</t>
+          <t>7,92; 10,53</t>
         </is>
       </c>
     </row>
@@ -1394,32 +1394,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>10,3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>10,9</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>10,41</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>9,47</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>11,2</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>9,75</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10,3</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>10,9</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>10,41</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1447,47 +1447,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>7,36; 10,76</t>
+          <t>9,05; 11,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>10,42; 12,44</t>
+          <t>9,83; 12,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,77; 10,75</t>
+          <t>8,73; 11,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9,06; 11,45</t>
+          <t>7,57; 10,61</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,83; 12,12</t>
+          <t>10,38; 12,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,67; 11,42</t>
+          <t>8,74; 10,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,91; 10,8</t>
+          <t>8,85; 10,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,31; 11,81</t>
+          <t>10,38; 11,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,17; 10,84</t>
+          <t>9,17; 10,79</t>
         </is>
       </c>
     </row>
@@ -1504,32 +1504,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>11,28</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11,14</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9,35</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>11,21</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>11,3</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>9,71</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>11,28</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>11,14</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>9,35</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1557,47 +1557,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,38; 11,96</t>
+          <t>10,65; 11,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10,8; 12,08</t>
+          <t>10,68; 11,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,12; 10,29</t>
+          <t>8,71; 9,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,67; 11,81</t>
+          <t>10,37; 11,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,69; 11,62</t>
+          <t>10,8; 11,99</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,73; 10,02</t>
+          <t>9,18; 10,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10,77; 11,69</t>
+          <t>10,81; 11,68</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,86; 11,66</t>
+          <t>10,87; 11,62</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,11; 9,98</t>
+          <t>9,06; 9,94</t>
         </is>
       </c>
     </row>
